--- a/data/availability/projects/palm-hills-developments/palm-hills-jirian.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-jirian.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -959,7 +959,6 @@
       <c r="G2" t="n">
         <v>294</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1016,7 +1015,6 @@
       <c r="G3" t="n">
         <v>294</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1073,7 +1071,6 @@
       <c r="G4" t="n">
         <v>294</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1130,7 +1127,6 @@
       <c r="G5" t="n">
         <v>196</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1187,7 +1183,6 @@
       <c r="G6" t="n">
         <v>283</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1244,7 +1239,6 @@
       <c r="G7" t="n">
         <v>176</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1301,7 +1295,6 @@
       <c r="G8" t="n">
         <v>174</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1358,7 +1351,6 @@
       <c r="G9" t="n">
         <v>176</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1415,7 +1407,6 @@
       <c r="G10" t="n">
         <v>176</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1472,7 +1463,6 @@
       <c r="G11" t="n">
         <v>174</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1529,7 +1519,6 @@
       <c r="G12" t="n">
         <v>196</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1586,7 +1575,6 @@
       <c r="G13" t="n">
         <v>196</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1643,7 +1631,6 @@
       <c r="G14" t="n">
         <v>196</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1700,7 +1687,6 @@
       <c r="G15" t="n">
         <v>196</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1757,7 +1743,6 @@
       <c r="G16" t="n">
         <v>174</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1814,7 +1799,6 @@
       <c r="G17" t="n">
         <v>176</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1871,7 +1855,6 @@
       <c r="G18" t="n">
         <v>174</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1928,7 +1911,6 @@
       <c r="G19" t="n">
         <v>174</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1985,7 +1967,6 @@
       <c r="G20" t="n">
         <v>174</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2042,7 +2023,6 @@
       <c r="G21" t="n">
         <v>176</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2099,7 +2079,6 @@
       <c r="G22" t="n">
         <v>196</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2156,7 +2135,6 @@
       <c r="G23" t="n">
         <v>196</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2189,7 +2167,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2213,7 +2191,6 @@
       <c r="G24" t="n">
         <v>159</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2246,7 +2223,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2270,7 +2247,6 @@
       <c r="G25" t="n">
         <v>106</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2303,7 +2279,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2327,7 +2303,6 @@
       <c r="G26" t="n">
         <v>106</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2360,7 +2335,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2384,7 +2359,6 @@
       <c r="G27" t="n">
         <v>159</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2417,7 +2391,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2441,7 +2415,6 @@
       <c r="G28" t="n">
         <v>158</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2474,7 +2447,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2498,7 +2471,6 @@
       <c r="G29" t="n">
         <v>159</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2531,7 +2503,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2555,7 +2527,6 @@
       <c r="G30" t="n">
         <v>106</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2588,7 +2559,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2612,7 +2583,6 @@
       <c r="G31" t="n">
         <v>106</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2645,7 +2615,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,7 +2639,6 @@
       <c r="G32" t="n">
         <v>159</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2702,7 +2671,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2726,7 +2695,6 @@
       <c r="G33" t="n">
         <v>159</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2759,7 +2727,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2783,7 +2751,6 @@
       <c r="G34" t="n">
         <v>106</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2816,7 +2783,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2840,7 +2807,6 @@
       <c r="G35" t="n">
         <v>106</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2873,7 +2839,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2897,7 +2863,6 @@
       <c r="G36" t="n">
         <v>159</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2930,7 +2895,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2954,7 +2919,6 @@
       <c r="G37" t="n">
         <v>64</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2987,7 +2951,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3011,7 +2975,6 @@
       <c r="G38" t="n">
         <v>159</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3044,7 +3007,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3068,7 +3031,6 @@
       <c r="G39" t="n">
         <v>159</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3101,7 +3063,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3125,7 +3087,6 @@
       <c r="G40" t="n">
         <v>159</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3158,7 +3119,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3182,7 +3143,6 @@
       <c r="G41" t="n">
         <v>64</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3215,7 +3175,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3239,7 +3199,6 @@
       <c r="G42" t="n">
         <v>159</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3272,7 +3231,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3296,7 +3255,6 @@
       <c r="G43" t="n">
         <v>159</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3329,7 +3287,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3353,7 +3311,6 @@
       <c r="G44" t="n">
         <v>159</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3386,7 +3343,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3410,7 +3367,6 @@
       <c r="G45" t="n">
         <v>155</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3443,7 +3399,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3467,7 +3423,6 @@
       <c r="G46" t="n">
         <v>194</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3500,7 +3455,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3524,7 +3479,6 @@
       <c r="G47" t="n">
         <v>155</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3557,7 +3511,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3581,7 +3535,6 @@
       <c r="G48" t="n">
         <v>151</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3614,7 +3567,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3638,7 +3591,6 @@
       <c r="G49" t="n">
         <v>155</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3671,7 +3623,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3695,7 +3647,6 @@
       <c r="G50" t="n">
         <v>206</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3728,7 +3679,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3752,7 +3703,6 @@
       <c r="G51" t="n">
         <v>206</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3785,7 +3735,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3809,7 +3759,6 @@
       <c r="G52" t="n">
         <v>155</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3842,7 +3791,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3866,7 +3815,6 @@
       <c r="G53" t="n">
         <v>159</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3899,7 +3847,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3923,7 +3871,6 @@
       <c r="G54" t="n">
         <v>159</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3956,7 +3903,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3980,7 +3927,6 @@
       <c r="G55" t="n">
         <v>159</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4013,7 +3959,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4037,7 +3983,6 @@
       <c r="G56" t="n">
         <v>106</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4070,7 +4015,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4094,7 +4039,6 @@
       <c r="G57" t="n">
         <v>159</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4127,7 +4071,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4151,7 +4095,6 @@
       <c r="G58" t="n">
         <v>159</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4184,7 +4127,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4208,7 +4151,6 @@
       <c r="G59" t="n">
         <v>159</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4241,7 +4183,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4265,7 +4207,6 @@
       <c r="G60" t="n">
         <v>159</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4298,7 +4239,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4322,7 +4263,6 @@
       <c r="G61" t="n">
         <v>159</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4355,7 +4295,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4379,7 +4319,6 @@
       <c r="G62" t="n">
         <v>159</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4412,7 +4351,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4436,7 +4375,6 @@
       <c r="G63" t="n">
         <v>159</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4469,7 +4407,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4493,7 +4431,6 @@
       <c r="G64" t="n">
         <v>159</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4526,7 +4463,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4550,7 +4487,6 @@
       <c r="G65" t="n">
         <v>152</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4583,7 +4519,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4607,7 +4543,6 @@
       <c r="G66" t="n">
         <v>159</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4640,7 +4575,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4664,7 +4599,6 @@
       <c r="G67" t="n">
         <v>106</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4697,7 +4631,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4721,7 +4655,6 @@
       <c r="G68" t="n">
         <v>106</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4754,7 +4687,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4778,7 +4711,6 @@
       <c r="G69" t="n">
         <v>159</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4811,7 +4743,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4835,7 +4767,6 @@
       <c r="G70" t="n">
         <v>159</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4868,7 +4799,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4892,7 +4823,6 @@
       <c r="G71" t="n">
         <v>106</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4925,7 +4855,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4949,7 +4879,6 @@
       <c r="G72" t="n">
         <v>106</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4982,7 +4911,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5006,7 +4935,6 @@
       <c r="G73" t="n">
         <v>159</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5039,7 +4967,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5063,7 +4991,6 @@
       <c r="G74" t="n">
         <v>159</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5096,7 +5023,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5120,7 +5047,6 @@
       <c r="G75" t="n">
         <v>159</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5153,7 +5079,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5177,7 +5103,6 @@
       <c r="G76" t="n">
         <v>159</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5210,7 +5135,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5234,7 +5159,6 @@
       <c r="G77" t="n">
         <v>159</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5267,7 +5191,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5291,7 +5215,6 @@
       <c r="G78" t="n">
         <v>159</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5324,7 +5247,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5348,7 +5271,6 @@
       <c r="G79" t="n">
         <v>159</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5381,7 +5303,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5405,7 +5327,6 @@
       <c r="G80" t="n">
         <v>159</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5438,7 +5359,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5462,7 +5383,6 @@
       <c r="G81" t="n">
         <v>159</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5495,7 +5415,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5519,7 +5439,6 @@
       <c r="G82" t="n">
         <v>155</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5552,7 +5471,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5576,7 +5495,6 @@
       <c r="G83" t="n">
         <v>194</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5609,7 +5527,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5633,7 +5551,6 @@
       <c r="G84" t="n">
         <v>194</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5666,7 +5583,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5690,7 +5607,6 @@
       <c r="G85" t="n">
         <v>155</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5723,7 +5639,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5747,7 +5663,6 @@
       <c r="G86" t="n">
         <v>152</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5780,7 +5695,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5804,7 +5719,6 @@
       <c r="G87" t="n">
         <v>151</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5837,7 +5751,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5861,7 +5775,6 @@
       <c r="G88" t="n">
         <v>159</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5894,7 +5807,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5918,7 +5831,6 @@
       <c r="G89" t="n">
         <v>106</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5951,7 +5863,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5975,7 +5887,6 @@
       <c r="G90" t="n">
         <v>106</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6008,7 +5919,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6032,7 +5943,6 @@
       <c r="G91" t="n">
         <v>159</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6065,7 +5975,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6089,7 +5999,6 @@
       <c r="G92" t="n">
         <v>159</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6122,7 +6031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6146,7 +6055,6 @@
       <c r="G93" t="n">
         <v>106</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6179,7 +6087,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6203,7 +6111,6 @@
       <c r="G94" t="n">
         <v>106</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6236,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6260,7 +6167,6 @@
       <c r="G95" t="n">
         <v>159</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6293,7 +6199,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6317,7 +6223,6 @@
       <c r="G96" t="n">
         <v>159</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6350,7 +6255,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6374,7 +6279,6 @@
       <c r="G97" t="n">
         <v>106</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6407,7 +6311,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6431,7 +6335,6 @@
       <c r="G98" t="n">
         <v>159</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6464,7 +6367,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6488,7 +6391,6 @@
       <c r="G99" t="n">
         <v>159</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6521,7 +6423,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6545,7 +6447,6 @@
       <c r="G100" t="n">
         <v>159</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6578,7 +6479,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6602,7 +6503,6 @@
       <c r="G101" t="n">
         <v>159</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6635,7 +6535,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6659,7 +6559,6 @@
       <c r="G102" t="n">
         <v>159</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6692,7 +6591,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6716,7 +6615,6 @@
       <c r="G103" t="n">
         <v>194</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6749,7 +6647,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6773,7 +6671,6 @@
       <c r="G104" t="n">
         <v>151</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6830,7 +6727,6 @@
       <c r="G105" t="n">
         <v>338</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6887,7 +6783,6 @@
       <c r="G106" t="n">
         <v>405</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6944,7 +6839,6 @@
       <c r="G107" t="n">
         <v>405</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7001,7 +6895,6 @@
       <c r="G108" t="n">
         <v>405</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7058,7 +6951,6 @@
       <c r="G109" t="n">
         <v>294</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7115,7 +7007,6 @@
       <c r="G110" t="n">
         <v>294</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7172,7 +7063,6 @@
       <c r="G111" t="n">
         <v>294</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7229,7 +7119,6 @@
       <c r="G112" t="n">
         <v>294</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7286,7 +7175,6 @@
       <c r="G113" t="n">
         <v>294</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7343,7 +7231,6 @@
       <c r="G114" t="n">
         <v>196</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7400,7 +7287,6 @@
       <c r="G115" t="n">
         <v>196</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7457,7 +7343,6 @@
       <c r="G116" t="n">
         <v>196</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7514,7 +7399,6 @@
       <c r="G117" t="n">
         <v>196</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7571,7 +7455,6 @@
       <c r="G118" t="n">
         <v>196</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7628,7 +7511,6 @@
       <c r="G119" t="n">
         <v>196</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7685,7 +7567,6 @@
       <c r="G120" t="n">
         <v>196</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7742,7 +7623,6 @@
       <c r="G121" t="n">
         <v>196</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7799,7 +7679,6 @@
       <c r="G122" t="n">
         <v>196</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7856,7 +7735,6 @@
       <c r="G123" t="n">
         <v>196</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7889,7 +7767,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7913,7 +7791,6 @@
       <c r="G124" t="n">
         <v>155</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7946,7 +7823,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7970,7 +7847,6 @@
       <c r="G125" t="n">
         <v>206</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8003,7 +7879,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8027,7 +7903,6 @@
       <c r="G126" t="n">
         <v>155</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8060,7 +7935,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8084,7 +7959,6 @@
       <c r="G127" t="n">
         <v>159</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8117,7 +7991,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8141,7 +8015,6 @@
       <c r="G128" t="n">
         <v>159</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8174,7 +8047,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8198,7 +8071,6 @@
       <c r="G129" t="n">
         <v>159</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8231,7 +8103,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8255,7 +8127,6 @@
       <c r="G130" t="n">
         <v>159</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8288,7 +8159,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8312,7 +8183,6 @@
       <c r="G131" t="n">
         <v>159</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8345,7 +8215,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8369,7 +8239,6 @@
       <c r="G132" t="n">
         <v>159</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8402,7 +8271,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8426,7 +8295,6 @@
       <c r="G133" t="n">
         <v>106</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8459,7 +8327,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8483,7 +8351,6 @@
       <c r="G134" t="n">
         <v>106</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8516,7 +8383,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8540,7 +8407,6 @@
       <c r="G135" t="n">
         <v>158</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8573,7 +8439,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8597,7 +8463,6 @@
       <c r="G136" t="n">
         <v>159</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8630,7 +8495,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8654,7 +8519,6 @@
       <c r="G137" t="n">
         <v>106</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8687,7 +8551,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8711,7 +8575,6 @@
       <c r="G138" t="n">
         <v>106</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8744,7 +8607,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8768,7 +8631,6 @@
       <c r="G139" t="n">
         <v>158</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8801,7 +8663,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8825,7 +8687,6 @@
       <c r="G140" t="n">
         <v>159</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8858,7 +8719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8882,7 +8743,6 @@
       <c r="G141" t="n">
         <v>106</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8915,7 +8775,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8939,7 +8799,6 @@
       <c r="G142" t="n">
         <v>106</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8972,7 +8831,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8996,7 +8855,6 @@
       <c r="G143" t="n">
         <v>158</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9029,7 +8887,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9053,7 +8911,6 @@
       <c r="G144" t="n">
         <v>159</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9086,7 +8943,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9110,7 +8967,6 @@
       <c r="G145" t="n">
         <v>106</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9143,7 +8999,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9167,7 +9023,6 @@
       <c r="G146" t="n">
         <v>158</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9200,7 +9055,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9224,7 +9079,6 @@
       <c r="G147" t="n">
         <v>63</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9257,7 +9111,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9281,7 +9135,6 @@
       <c r="G148" t="n">
         <v>159</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9314,7 +9167,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9338,7 +9191,6 @@
       <c r="G149" t="n">
         <v>106</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9371,7 +9223,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9395,7 +9247,6 @@
       <c r="G150" t="n">
         <v>106</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9428,7 +9279,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9452,7 +9303,6 @@
       <c r="G151" t="n">
         <v>158</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9485,7 +9335,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9509,7 +9359,6 @@
       <c r="G152" t="n">
         <v>159</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9542,7 +9391,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9566,7 +9415,6 @@
       <c r="G153" t="n">
         <v>106</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9599,7 +9447,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9623,7 +9471,6 @@
       <c r="G154" t="n">
         <v>106</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9656,7 +9503,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9680,7 +9527,6 @@
       <c r="G155" t="n">
         <v>158</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9713,7 +9559,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9737,7 +9583,6 @@
       <c r="G156" t="n">
         <v>63</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9770,7 +9615,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9794,7 +9639,6 @@
       <c r="G157" t="n">
         <v>144</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9827,7 +9671,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9851,7 +9695,6 @@
       <c r="G158" t="n">
         <v>106</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9884,7 +9727,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9908,7 +9751,6 @@
       <c r="G159" t="n">
         <v>106</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9941,7 +9783,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9965,7 +9807,6 @@
       <c r="G160" t="n">
         <v>143</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9998,7 +9839,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10022,7 +9863,6 @@
       <c r="G161" t="n">
         <v>126</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10055,7 +9895,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10079,7 +9919,6 @@
       <c r="G162" t="n">
         <v>99</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10112,7 +9951,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10136,7 +9975,6 @@
       <c r="G163" t="n">
         <v>99</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10169,7 +10007,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10193,7 +10031,6 @@
       <c r="G164" t="n">
         <v>126</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10226,7 +10063,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10250,7 +10087,6 @@
       <c r="G165" t="n">
         <v>159</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10283,7 +10119,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10307,7 +10143,6 @@
       <c r="G166" t="n">
         <v>106</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10340,7 +10175,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10364,7 +10199,6 @@
       <c r="G167" t="n">
         <v>106</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10397,7 +10231,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10421,7 +10255,6 @@
       <c r="G168" t="n">
         <v>158</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10454,7 +10287,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10478,7 +10311,6 @@
       <c r="G169" t="n">
         <v>159</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10511,7 +10343,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10535,7 +10367,6 @@
       <c r="G170" t="n">
         <v>106</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10568,7 +10399,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10592,7 +10423,6 @@
       <c r="G171" t="n">
         <v>106</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10625,7 +10455,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10649,7 +10479,6 @@
       <c r="G172" t="n">
         <v>158</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10682,7 +10511,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10706,7 +10535,6 @@
       <c r="G173" t="n">
         <v>159</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10739,7 +10567,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10763,7 +10591,6 @@
       <c r="G174" t="n">
         <v>106</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10796,7 +10623,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10820,7 +10647,6 @@
       <c r="G175" t="n">
         <v>106</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10853,7 +10679,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10877,7 +10703,6 @@
       <c r="G176" t="n">
         <v>158</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10910,7 +10735,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10934,7 +10759,6 @@
       <c r="G177" t="n">
         <v>63</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10967,7 +10791,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10991,7 +10815,6 @@
       <c r="G178" t="n">
         <v>159</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11024,7 +10847,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11048,7 +10871,6 @@
       <c r="G179" t="n">
         <v>106</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11081,7 +10903,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11105,7 +10927,6 @@
       <c r="G180" t="n">
         <v>158</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11138,7 +10959,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11162,7 +10983,6 @@
       <c r="G181" t="n">
         <v>63</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11195,7 +11015,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11219,7 +11039,6 @@
       <c r="G182" t="n">
         <v>159</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11252,7 +11071,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11276,7 +11095,6 @@
       <c r="G183" t="n">
         <v>106</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11309,7 +11127,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11333,7 +11151,6 @@
       <c r="G184" t="n">
         <v>106</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11366,7 +11183,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11390,7 +11207,6 @@
       <c r="G185" t="n">
         <v>158</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11423,7 +11239,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11447,7 +11263,6 @@
       <c r="G186" t="n">
         <v>63</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11480,7 +11295,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11504,7 +11319,6 @@
       <c r="G187" t="n">
         <v>159</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11537,7 +11351,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11561,7 +11375,6 @@
       <c r="G188" t="n">
         <v>106</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11594,7 +11407,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11618,7 +11431,6 @@
       <c r="G189" t="n">
         <v>106</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11651,7 +11463,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11675,7 +11487,6 @@
       <c r="G190" t="n">
         <v>158</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11708,7 +11519,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11732,7 +11543,6 @@
       <c r="G191" t="n">
         <v>144</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11765,7 +11575,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11789,7 +11599,6 @@
       <c r="G192" t="n">
         <v>126</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11822,7 +11631,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11846,7 +11655,6 @@
       <c r="G193" t="n">
         <v>99</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11879,7 +11687,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11903,7 +11711,6 @@
       <c r="G194" t="n">
         <v>126</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11936,7 +11743,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11960,7 +11767,6 @@
       <c r="G195" t="n">
         <v>159</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11993,7 +11799,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12017,7 +11823,6 @@
       <c r="G196" t="n">
         <v>106</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12050,7 +11855,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12074,7 +11879,6 @@
       <c r="G197" t="n">
         <v>106</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12107,7 +11911,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12131,7 +11935,6 @@
       <c r="G198" t="n">
         <v>158</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12164,7 +11967,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12188,7 +11991,6 @@
       <c r="G199" t="n">
         <v>63</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12221,7 +12023,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12245,7 +12047,6 @@
       <c r="G200" t="n">
         <v>159</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12278,7 +12079,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12302,7 +12103,6 @@
       <c r="G201" t="n">
         <v>106</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12335,7 +12135,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12359,7 +12159,6 @@
       <c r="G202" t="n">
         <v>158</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12392,7 +12191,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12416,7 +12215,6 @@
       <c r="G203" t="n">
         <v>63</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12449,7 +12247,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12473,7 +12271,6 @@
       <c r="G204" t="n">
         <v>159</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12506,7 +12303,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12530,7 +12327,6 @@
       <c r="G205" t="n">
         <v>106</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12563,7 +12359,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12587,7 +12383,6 @@
       <c r="G206" t="n">
         <v>158</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12620,7 +12415,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12644,7 +12439,6 @@
       <c r="G207" t="n">
         <v>63</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12677,7 +12471,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12701,7 +12495,6 @@
       <c r="G208" t="n">
         <v>159</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12734,7 +12527,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12758,7 +12551,6 @@
       <c r="G209" t="n">
         <v>158</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12791,7 +12583,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12815,7 +12607,6 @@
       <c r="G210" t="n">
         <v>63</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12848,7 +12639,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12872,7 +12663,6 @@
       <c r="G211" t="n">
         <v>159</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12905,7 +12695,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12929,7 +12719,6 @@
       <c r="G212" t="n">
         <v>158</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12962,7 +12751,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12986,7 +12775,6 @@
       <c r="G213" t="n">
         <v>159</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13019,7 +12807,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13043,7 +12831,6 @@
       <c r="G214" t="n">
         <v>158</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13076,7 +12863,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13100,7 +12887,6 @@
       <c r="G215" t="n">
         <v>144</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13133,7 +12919,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13157,7 +12943,6 @@
       <c r="G216" t="n">
         <v>143</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13190,7 +12975,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13214,7 +12999,6 @@
       <c r="G217" t="n">
         <v>63</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13247,7 +13031,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13271,7 +13055,6 @@
       <c r="G218" t="n">
         <v>126</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13304,7 +13087,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13328,7 +13111,6 @@
       <c r="G219" t="n">
         <v>159</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13361,7 +13143,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13385,7 +13167,6 @@
       <c r="G220" t="n">
         <v>106</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13418,7 +13199,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13442,7 +13223,6 @@
       <c r="G221" t="n">
         <v>106</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13475,7 +13255,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13499,7 +13279,6 @@
       <c r="G222" t="n">
         <v>158</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13532,7 +13311,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13556,7 +13335,6 @@
       <c r="G223" t="n">
         <v>159</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13589,7 +13367,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13613,7 +13391,6 @@
       <c r="G224" t="n">
         <v>106</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13646,7 +13423,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13670,7 +13447,6 @@
       <c r="G225" t="n">
         <v>106</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13703,7 +13479,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13727,7 +13503,6 @@
       <c r="G226" t="n">
         <v>158</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13760,7 +13535,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13784,7 +13559,6 @@
       <c r="G227" t="n">
         <v>63</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13817,7 +13591,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13841,7 +13615,6 @@
       <c r="G228" t="n">
         <v>159</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13874,7 +13647,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13898,7 +13671,6 @@
       <c r="G229" t="n">
         <v>106</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13931,7 +13703,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13955,7 +13727,6 @@
       <c r="G230" t="n">
         <v>106</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13988,7 +13759,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14012,7 +13783,6 @@
       <c r="G231" t="n">
         <v>158</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14045,7 +13815,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14069,7 +13839,6 @@
       <c r="G232" t="n">
         <v>63</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14102,7 +13871,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14126,7 +13895,6 @@
       <c r="G233" t="n">
         <v>159</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14159,7 +13927,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14183,7 +13951,6 @@
       <c r="G234" t="n">
         <v>106</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14216,7 +13983,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14240,7 +14007,6 @@
       <c r="G235" t="n">
         <v>106</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14273,7 +14039,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14297,7 +14063,6 @@
       <c r="G236" t="n">
         <v>158</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14330,7 +14095,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14354,7 +14119,6 @@
       <c r="G237" t="n">
         <v>63</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14387,7 +14151,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14411,7 +14175,6 @@
       <c r="G238" t="n">
         <v>159</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14444,7 +14207,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14468,7 +14231,6 @@
       <c r="G239" t="n">
         <v>106</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14501,7 +14263,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14525,7 +14287,6 @@
       <c r="G240" t="n">
         <v>158</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14558,7 +14319,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14582,7 +14343,6 @@
       <c r="G241" t="n">
         <v>63</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14615,7 +14375,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14639,7 +14399,6 @@
       <c r="G242" t="n">
         <v>159</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14672,7 +14431,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14696,7 +14455,6 @@
       <c r="G243" t="n">
         <v>106</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14729,7 +14487,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14753,7 +14511,6 @@
       <c r="G244" t="n">
         <v>158</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14786,7 +14543,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14810,7 +14567,6 @@
       <c r="G245" t="n">
         <v>144</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14843,7 +14599,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14867,7 +14623,6 @@
       <c r="G246" t="n">
         <v>106</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14900,7 +14655,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14924,7 +14679,6 @@
       <c r="G247" t="n">
         <v>143</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14957,7 +14711,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14981,7 +14735,6 @@
       <c r="G248" t="n">
         <v>63</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15014,7 +14767,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15038,7 +14791,6 @@
       <c r="G249" t="n">
         <v>126</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15071,7 +14823,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15095,7 +14847,6 @@
       <c r="G250" t="n">
         <v>126</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15128,7 +14879,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15152,7 +14903,6 @@
       <c r="G251" t="n">
         <v>159</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15185,7 +14935,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15209,7 +14959,6 @@
       <c r="G252" t="n">
         <v>106</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15242,7 +14991,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15266,7 +15015,6 @@
       <c r="G253" t="n">
         <v>106</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15299,7 +15047,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15323,7 +15071,6 @@
       <c r="G254" t="n">
         <v>158</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15356,7 +15103,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15380,7 +15127,6 @@
       <c r="G255" t="n">
         <v>159</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15413,7 +15159,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15437,7 +15183,6 @@
       <c r="G256" t="n">
         <v>106</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15470,7 +15215,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15494,7 +15239,6 @@
       <c r="G257" t="n">
         <v>106</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15527,7 +15271,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15551,7 +15295,6 @@
       <c r="G258" t="n">
         <v>158</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15584,7 +15327,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15608,7 +15351,6 @@
       <c r="G259" t="n">
         <v>63</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15641,7 +15383,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15665,7 +15407,6 @@
       <c r="G260" t="n">
         <v>159</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15698,7 +15439,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15722,7 +15463,6 @@
       <c r="G261" t="n">
         <v>106</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15755,7 +15495,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15779,7 +15519,6 @@
       <c r="G262" t="n">
         <v>106</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15812,7 +15551,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15836,7 +15575,6 @@
       <c r="G263" t="n">
         <v>158</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15869,7 +15607,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15893,7 +15631,6 @@
       <c r="G264" t="n">
         <v>63</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15926,7 +15663,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15950,7 +15687,6 @@
       <c r="G265" t="n">
         <v>159</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15983,7 +15719,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16007,7 +15743,6 @@
       <c r="G266" t="n">
         <v>106</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16040,7 +15775,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16064,7 +15799,6 @@
       <c r="G267" t="n">
         <v>106</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16097,7 +15831,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16121,7 +15855,6 @@
       <c r="G268" t="n">
         <v>158</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16154,7 +15887,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16178,7 +15911,6 @@
       <c r="G269" t="n">
         <v>63</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16211,7 +15943,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16235,7 +15967,6 @@
       <c r="G270" t="n">
         <v>159</v>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16268,7 +15999,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16292,7 +16023,6 @@
       <c r="G271" t="n">
         <v>106</v>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16325,7 +16055,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -16349,7 +16079,6 @@
       <c r="G272" t="n">
         <v>158</v>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16382,7 +16111,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -16406,7 +16135,6 @@
       <c r="G273" t="n">
         <v>63</v>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16439,7 +16167,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16463,7 +16191,6 @@
       <c r="G274" t="n">
         <v>159</v>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16496,7 +16223,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16520,7 +16247,6 @@
       <c r="G275" t="n">
         <v>158</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16553,7 +16279,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16577,7 +16303,6 @@
       <c r="G276" t="n">
         <v>63</v>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16610,7 +16335,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16634,7 +16359,6 @@
       <c r="G277" t="n">
         <v>144</v>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16667,7 +16391,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16691,7 +16415,6 @@
       <c r="G278" t="n">
         <v>143</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16724,7 +16447,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16748,7 +16471,6 @@
       <c r="G279" t="n">
         <v>126</v>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16781,7 +16503,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16805,7 +16527,6 @@
       <c r="G280" t="n">
         <v>126</v>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16838,7 +16559,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16862,7 +16583,6 @@
       <c r="G281" t="n">
         <v>159</v>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16895,7 +16615,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16919,7 +16639,6 @@
       <c r="G282" t="n">
         <v>159</v>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16952,7 +16671,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16976,7 +16695,6 @@
       <c r="G283" t="n">
         <v>159</v>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17009,7 +16727,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17033,7 +16751,6 @@
       <c r="G284" t="n">
         <v>159</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17066,7 +16783,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17090,7 +16807,6 @@
       <c r="G285" t="n">
         <v>159</v>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17123,7 +16839,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17147,7 +16863,6 @@
       <c r="G286" t="n">
         <v>159</v>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17180,7 +16895,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17204,7 +16919,6 @@
       <c r="G287" t="n">
         <v>159</v>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17237,7 +16951,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -17261,7 +16975,6 @@
       <c r="G288" t="n">
         <v>159</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17294,7 +17007,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -17318,7 +17031,6 @@
       <c r="G289" t="n">
         <v>159</v>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17351,7 +17063,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -17375,7 +17087,6 @@
       <c r="G290" t="n">
         <v>159</v>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17408,7 +17119,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -17432,7 +17143,6 @@
       <c r="G291" t="n">
         <v>155</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17465,7 +17175,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -17489,7 +17199,6 @@
       <c r="G292" t="n">
         <v>159</v>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17522,7 +17231,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17546,7 +17255,6 @@
       <c r="G293" t="n">
         <v>159</v>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17579,7 +17287,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17603,7 +17311,6 @@
       <c r="G294" t="n">
         <v>64</v>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17636,7 +17343,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17660,7 +17367,6 @@
       <c r="G295" t="n">
         <v>159</v>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17693,7 +17399,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17717,7 +17423,6 @@
       <c r="G296" t="n">
         <v>159</v>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17750,7 +17455,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17774,7 +17479,6 @@
       <c r="G297" t="n">
         <v>159</v>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17807,7 +17511,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17831,7 +17535,6 @@
       <c r="G298" t="n">
         <v>159</v>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17864,7 +17567,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17888,7 +17591,6 @@
       <c r="G299" t="n">
         <v>159</v>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17921,7 +17623,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17945,7 +17647,6 @@
       <c r="G300" t="n">
         <v>159</v>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17978,7 +17679,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18002,7 +17703,6 @@
       <c r="G301" t="n">
         <v>159</v>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18035,7 +17735,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18059,7 +17759,6 @@
       <c r="G302" t="n">
         <v>159</v>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18092,7 +17791,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18116,7 +17815,6 @@
       <c r="G303" t="n">
         <v>159</v>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18149,7 +17847,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -18173,7 +17871,6 @@
       <c r="G304" t="n">
         <v>159</v>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18206,7 +17903,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -18230,7 +17927,6 @@
       <c r="G305" t="n">
         <v>64</v>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18263,7 +17959,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -18287,7 +17983,6 @@
       <c r="G306" t="n">
         <v>194</v>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18320,7 +18015,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -18344,7 +18039,6 @@
       <c r="G307" t="n">
         <v>155</v>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18377,7 +18071,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -18401,7 +18095,6 @@
       <c r="G308" t="n">
         <v>64</v>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18434,7 +18127,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -18458,7 +18151,6 @@
       <c r="G309" t="n">
         <v>152</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18491,7 +18183,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -18515,7 +18207,6 @@
       <c r="G310" t="n">
         <v>151</v>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18548,7 +18239,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18572,7 +18263,6 @@
       <c r="G311" t="n">
         <v>159</v>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18605,7 +18295,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18629,7 +18319,6 @@
       <c r="G312" t="n">
         <v>106</v>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18662,7 +18351,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18686,7 +18375,6 @@
       <c r="G313" t="n">
         <v>159</v>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18719,7 +18407,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18743,7 +18431,6 @@
       <c r="G314" t="n">
         <v>159</v>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18776,7 +18463,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18800,7 +18487,6 @@
       <c r="G315" t="n">
         <v>159</v>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18833,7 +18519,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18857,7 +18543,6 @@
       <c r="G316" t="n">
         <v>64</v>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18890,7 +18575,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18914,7 +18599,6 @@
       <c r="G317" t="n">
         <v>159</v>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18947,7 +18631,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18971,7 +18655,6 @@
       <c r="G318" t="n">
         <v>159</v>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19004,7 +18687,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19028,7 +18711,6 @@
       <c r="G319" t="n">
         <v>159</v>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19061,7 +18743,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19085,7 +18767,6 @@
       <c r="G320" t="n">
         <v>159</v>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19118,7 +18799,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -19142,7 +18823,6 @@
       <c r="G321" t="n">
         <v>64</v>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19175,7 +18855,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -19199,7 +18879,6 @@
       <c r="G322" t="n">
         <v>159</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19232,7 +18911,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -19256,7 +18935,6 @@
       <c r="G323" t="n">
         <v>159</v>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19289,7 +18967,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -19313,7 +18991,6 @@
       <c r="G324" t="n">
         <v>159</v>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19346,7 +19023,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -19370,7 +19047,6 @@
       <c r="G325" t="n">
         <v>155</v>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19403,7 +19079,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -19427,7 +19103,6 @@
       <c r="G326" t="n">
         <v>194</v>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19460,7 +19135,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -19484,7 +19159,6 @@
       <c r="G327" t="n">
         <v>155</v>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19517,7 +19191,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -19541,7 +19215,6 @@
       <c r="G328" t="n">
         <v>152</v>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19574,7 +19247,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -19598,7 +19271,6 @@
       <c r="G329" t="n">
         <v>151</v>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19631,7 +19303,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19655,7 +19327,6 @@
       <c r="G330" t="n">
         <v>159</v>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19688,7 +19359,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19712,7 +19383,6 @@
       <c r="G331" t="n">
         <v>159</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19745,7 +19415,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19769,7 +19439,6 @@
       <c r="G332" t="n">
         <v>159</v>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19802,7 +19471,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19826,7 +19495,6 @@
       <c r="G333" t="n">
         <v>159</v>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19859,7 +19527,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19883,7 +19551,6 @@
       <c r="G334" t="n">
         <v>64</v>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19916,7 +19583,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19940,7 +19607,6 @@
       <c r="G335" t="n">
         <v>159</v>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19973,7 +19639,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19997,7 +19663,6 @@
       <c r="G336" t="n">
         <v>159</v>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20030,7 +19695,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -20054,7 +19719,6 @@
       <c r="G337" t="n">
         <v>159</v>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20087,7 +19751,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -20111,7 +19775,6 @@
       <c r="G338" t="n">
         <v>155</v>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20144,7 +19807,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -20168,7 +19831,6 @@
       <c r="G339" t="n">
         <v>194</v>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20201,7 +19863,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -20225,7 +19887,6 @@
       <c r="G340" t="n">
         <v>151</v>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20258,7 +19919,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -20282,7 +19943,6 @@
       <c r="G341" t="n">
         <v>159</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20315,7 +19975,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -20339,7 +19999,6 @@
       <c r="G342" t="n">
         <v>106</v>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20372,7 +20031,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -20396,7 +20055,6 @@
       <c r="G343" t="n">
         <v>159</v>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20429,7 +20087,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -20453,7 +20111,6 @@
       <c r="G344" t="n">
         <v>159</v>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20486,7 +20143,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -20510,7 +20167,6 @@
       <c r="G345" t="n">
         <v>159</v>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20543,7 +20199,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20567,7 +20223,6 @@
       <c r="G346" t="n">
         <v>64</v>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20600,7 +20255,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -20624,7 +20279,6 @@
       <c r="G347" t="n">
         <v>159</v>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20657,7 +20311,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -20681,7 +20335,6 @@
       <c r="G348" t="n">
         <v>159</v>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20714,7 +20367,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20738,7 +20391,6 @@
       <c r="G349" t="n">
         <v>64</v>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20771,7 +20423,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20795,7 +20447,6 @@
       <c r="G350" t="n">
         <v>159</v>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20828,7 +20479,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20852,7 +20503,6 @@
       <c r="G351" t="n">
         <v>159</v>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20885,7 +20535,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20909,7 +20559,6 @@
       <c r="G352" t="n">
         <v>64</v>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20942,7 +20591,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20966,7 +20615,6 @@
       <c r="G353" t="n">
         <v>159</v>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20999,7 +20647,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -21023,7 +20671,6 @@
       <c r="G354" t="n">
         <v>159</v>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21056,7 +20703,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -21080,7 +20727,6 @@
       <c r="G355" t="n">
         <v>159</v>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21113,7 +20759,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -21137,7 +20783,6 @@
       <c r="G356" t="n">
         <v>194</v>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21170,7 +20815,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -21194,7 +20839,6 @@
       <c r="G357" t="n">
         <v>152</v>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21227,7 +20871,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -21251,7 +20895,6 @@
       <c r="G358" t="n">
         <v>151</v>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21284,7 +20927,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -21308,7 +20951,6 @@
       <c r="G359" t="n">
         <v>159</v>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21341,7 +20983,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -21365,7 +21007,6 @@
       <c r="G360" t="n">
         <v>106</v>
       </c>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21398,7 +21039,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -21422,7 +21063,6 @@
       <c r="G361" t="n">
         <v>106</v>
       </c>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21455,7 +21095,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -21479,7 +21119,6 @@
       <c r="G362" t="n">
         <v>159</v>
       </c>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21512,7 +21151,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -21536,7 +21175,6 @@
       <c r="G363" t="n">
         <v>159</v>
       </c>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21569,7 +21207,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -21593,7 +21231,6 @@
       <c r="G364" t="n">
         <v>159</v>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21626,7 +21263,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -21650,7 +21287,6 @@
       <c r="G365" t="n">
         <v>159</v>
       </c>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21683,7 +21319,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -21707,7 +21343,6 @@
       <c r="G366" t="n">
         <v>159</v>
       </c>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21740,7 +21375,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -21764,7 +21399,6 @@
       <c r="G367" t="n">
         <v>159</v>
       </c>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21797,7 +21431,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21821,7 +21455,6 @@
       <c r="G368" t="n">
         <v>159</v>
       </c>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21854,7 +21487,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21878,7 +21511,6 @@
       <c r="G369" t="n">
         <v>159</v>
       </c>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21911,7 +21543,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21935,7 +21567,6 @@
       <c r="G370" t="n">
         <v>159</v>
       </c>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21968,7 +21599,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21992,7 +21623,6 @@
       <c r="G371" t="n">
         <v>159</v>
       </c>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22025,7 +21655,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -22049,7 +21679,6 @@
       <c r="G372" t="n">
         <v>159</v>
       </c>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22082,7 +21711,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -22106,7 +21735,6 @@
       <c r="G373" t="n">
         <v>155</v>
       </c>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22139,7 +21767,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -22163,7 +21791,6 @@
       <c r="G374" t="n">
         <v>194</v>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22196,7 +21823,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -22220,7 +21847,6 @@
       <c r="G375" t="n">
         <v>194</v>
       </c>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22253,7 +21879,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -22277,7 +21903,6 @@
       <c r="G376" t="n">
         <v>155</v>
       </c>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22310,7 +21935,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -22334,7 +21959,6 @@
       <c r="G377" t="n">
         <v>152</v>
       </c>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22367,7 +21991,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -22391,7 +22015,6 @@
       <c r="G378" t="n">
         <v>151</v>
       </c>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22424,7 +22047,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -22448,7 +22071,6 @@
       <c r="G379" t="n">
         <v>159</v>
       </c>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22481,7 +22103,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -22505,7 +22127,6 @@
       <c r="G380" t="n">
         <v>106</v>
       </c>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22538,7 +22159,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -22562,7 +22183,6 @@
       <c r="G381" t="n">
         <v>106</v>
       </c>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22595,7 +22215,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -22619,7 +22239,6 @@
       <c r="G382" t="n">
         <v>159</v>
       </c>
-      <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22652,7 +22271,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -22676,7 +22295,6 @@
       <c r="G383" t="n">
         <v>159</v>
       </c>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22709,7 +22327,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -22733,7 +22351,6 @@
       <c r="G384" t="n">
         <v>159</v>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22766,7 +22383,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -22790,7 +22407,6 @@
       <c r="G385" t="n">
         <v>159</v>
       </c>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22823,7 +22439,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -22847,7 +22463,6 @@
       <c r="G386" t="n">
         <v>159</v>
       </c>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22880,7 +22495,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22904,7 +22519,6 @@
       <c r="G387" t="n">
         <v>159</v>
       </c>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22937,7 +22551,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22961,7 +22575,6 @@
       <c r="G388" t="n">
         <v>159</v>
       </c>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22994,7 +22607,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -23018,7 +22631,6 @@
       <c r="G389" t="n">
         <v>159</v>
       </c>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23051,7 +22663,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -23075,7 +22687,6 @@
       <c r="G390" t="n">
         <v>159</v>
       </c>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23108,7 +22719,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -23132,7 +22743,6 @@
       <c r="G391" t="n">
         <v>64</v>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23165,7 +22775,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -23189,7 +22799,6 @@
       <c r="G392" t="n">
         <v>159</v>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23222,7 +22831,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -23246,7 +22855,6 @@
       <c r="G393" t="n">
         <v>159</v>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23279,7 +22887,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -23303,7 +22911,6 @@
       <c r="G394" t="n">
         <v>155</v>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23336,7 +22943,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -23360,7 +22967,6 @@
       <c r="G395" t="n">
         <v>155</v>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23393,7 +22999,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -23417,7 +23023,6 @@
       <c r="G396" t="n">
         <v>151</v>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23450,7 +23055,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -23474,7 +23079,6 @@
       <c r="G397" t="n">
         <v>163</v>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23507,7 +23111,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -23531,7 +23135,6 @@
       <c r="G398" t="n">
         <v>220</v>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23564,7 +23167,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -23588,7 +23191,6 @@
       <c r="G399" t="n">
         <v>220</v>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23621,7 +23223,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -23645,7 +23247,6 @@
       <c r="G400" t="n">
         <v>163</v>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23678,7 +23279,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -23702,7 +23303,6 @@
       <c r="G401" t="n">
         <v>163</v>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23735,7 +23335,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -23759,7 +23359,6 @@
       <c r="G402" t="n">
         <v>163</v>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23792,7 +23391,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -23816,7 +23415,6 @@
       <c r="G403" t="n">
         <v>163</v>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23849,7 +23447,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -23873,7 +23471,6 @@
       <c r="G404" t="n">
         <v>163</v>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23906,7 +23503,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -23930,7 +23527,6 @@
       <c r="G405" t="n">
         <v>163</v>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23963,7 +23559,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -23987,7 +23583,6 @@
       <c r="G406" t="n">
         <v>163</v>
       </c>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24020,7 +23615,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -24044,7 +23639,6 @@
       <c r="G407" t="n">
         <v>163</v>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24077,7 +23671,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -24101,7 +23695,6 @@
       <c r="G408" t="n">
         <v>163</v>
       </c>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24134,7 +23727,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -24158,7 +23751,6 @@
       <c r="G409" t="n">
         <v>163</v>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24191,7 +23783,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -24215,7 +23807,6 @@
       <c r="G410" t="n">
         <v>163</v>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24248,7 +23839,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -24272,7 +23863,6 @@
       <c r="G411" t="n">
         <v>163</v>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24305,7 +23895,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -24329,7 +23919,6 @@
       <c r="G412" t="n">
         <v>163</v>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24362,7 +23951,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -24386,7 +23975,6 @@
       <c r="G413" t="n">
         <v>163</v>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24419,7 +24007,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -24443,7 +24031,6 @@
       <c r="G414" t="n">
         <v>163</v>
       </c>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24476,7 +24063,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -24500,7 +24087,6 @@
       <c r="G415" t="n">
         <v>163</v>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24533,7 +24119,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -24557,7 +24143,6 @@
       <c r="G416" t="n">
         <v>163</v>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24590,7 +24175,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -24614,7 +24199,6 @@
       <c r="G417" t="n">
         <v>206</v>
       </c>
-      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24647,7 +24231,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -24671,7 +24255,6 @@
       <c r="G418" t="n">
         <v>163</v>
       </c>
-      <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24704,7 +24287,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -24728,7 +24311,6 @@
       <c r="G419" t="n">
         <v>220</v>
       </c>
-      <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24761,7 +24343,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -24785,7 +24367,6 @@
       <c r="G420" t="n">
         <v>220</v>
       </c>
-      <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24818,7 +24399,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -24842,7 +24423,6 @@
       <c r="G421" t="n">
         <v>163</v>
       </c>
-      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24875,7 +24455,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -24899,7 +24479,6 @@
       <c r="G422" t="n">
         <v>163</v>
       </c>
-      <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24932,7 +24511,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -24956,7 +24535,6 @@
       <c r="G423" t="n">
         <v>163</v>
       </c>
-      <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24989,7 +24567,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -25013,7 +24591,6 @@
       <c r="G424" t="n">
         <v>163</v>
       </c>
-      <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25046,7 +24623,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -25070,7 +24647,6 @@
       <c r="G425" t="n">
         <v>163</v>
       </c>
-      <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25103,7 +24679,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -25127,7 +24703,6 @@
       <c r="G426" t="n">
         <v>163</v>
       </c>
-      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25160,7 +24735,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -25184,7 +24759,6 @@
       <c r="G427" t="n">
         <v>163</v>
       </c>
-      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25217,7 +24791,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -25241,7 +24815,6 @@
       <c r="G428" t="n">
         <v>163</v>
       </c>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25274,7 +24847,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -25298,7 +24871,6 @@
       <c r="G429" t="n">
         <v>163</v>
       </c>
-      <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25331,7 +24903,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -25355,7 +24927,6 @@
       <c r="G430" t="n">
         <v>163</v>
       </c>
-      <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25388,7 +24959,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -25412,7 +24983,6 @@
       <c r="G431" t="n">
         <v>163</v>
       </c>
-      <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25445,7 +25015,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -25469,7 +25039,6 @@
       <c r="G432" t="n">
         <v>163</v>
       </c>
-      <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25502,7 +25071,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -25526,7 +25095,6 @@
       <c r="G433" t="n">
         <v>163</v>
       </c>
-      <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25559,7 +25127,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -25583,7 +25151,6 @@
       <c r="G434" t="n">
         <v>220</v>
       </c>
-      <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25616,7 +25183,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -25640,7 +25207,6 @@
       <c r="G435" t="n">
         <v>220</v>
       </c>
-      <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25673,7 +25239,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -25697,7 +25263,6 @@
       <c r="G436" t="n">
         <v>163</v>
       </c>
-      <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25730,7 +25295,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -25754,7 +25319,6 @@
       <c r="G437" t="n">
         <v>163</v>
       </c>
-      <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25787,7 +25351,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -25811,7 +25375,6 @@
       <c r="G438" t="n">
         <v>163</v>
       </c>
-      <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25844,7 +25407,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -25868,7 +25431,6 @@
       <c r="G439" t="n">
         <v>163</v>
       </c>
-      <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25901,7 +25463,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -25925,7 +25487,6 @@
       <c r="G440" t="n">
         <v>163</v>
       </c>
-      <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25958,7 +25519,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -25982,7 +25543,6 @@
       <c r="G441" t="n">
         <v>163</v>
       </c>
-      <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26015,7 +25575,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -26039,7 +25599,6 @@
       <c r="G442" t="n">
         <v>163</v>
       </c>
-      <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26072,7 +25631,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -26096,7 +25655,6 @@
       <c r="G443" t="n">
         <v>121</v>
       </c>
-      <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26129,7 +25687,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -26153,7 +25711,6 @@
       <c r="G444" t="n">
         <v>107</v>
       </c>
-      <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26186,7 +25743,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -26210,7 +25767,6 @@
       <c r="G445" t="n">
         <v>137</v>
       </c>
-      <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26243,7 +25799,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -26267,7 +25823,6 @@
       <c r="G446" t="n">
         <v>62</v>
       </c>
-      <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26300,7 +25855,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -26324,7 +25879,6 @@
       <c r="G447" t="n">
         <v>121</v>
       </c>
-      <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26357,7 +25911,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -26381,7 +25935,6 @@
       <c r="G448" t="n">
         <v>107</v>
       </c>
-      <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26414,7 +25967,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -26438,7 +25991,6 @@
       <c r="G449" t="n">
         <v>107</v>
       </c>
-      <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26471,7 +26023,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -26495,7 +26047,6 @@
       <c r="G450" t="n">
         <v>137</v>
       </c>
-      <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26528,7 +26079,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -26552,7 +26103,6 @@
       <c r="G451" t="n">
         <v>62</v>
       </c>
-      <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26585,7 +26135,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -26609,7 +26159,6 @@
       <c r="G452" t="n">
         <v>121</v>
       </c>
-      <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26642,7 +26191,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -26666,7 +26215,6 @@
       <c r="G453" t="n">
         <v>137</v>
       </c>
-      <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26699,7 +26247,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -26723,7 +26271,6 @@
       <c r="G454" t="n">
         <v>62</v>
       </c>
-      <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26756,7 +26303,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -26780,7 +26327,6 @@
       <c r="G455" t="n">
         <v>121</v>
       </c>
-      <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26813,7 +26359,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -26837,7 +26383,6 @@
       <c r="G456" t="n">
         <v>137</v>
       </c>
-      <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26870,7 +26415,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -26894,7 +26439,6 @@
       <c r="G457" t="n">
         <v>62</v>
       </c>
-      <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26927,7 +26471,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -26951,7 +26495,6 @@
       <c r="G458" t="n">
         <v>137</v>
       </c>
-      <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26984,7 +26527,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -27008,7 +26551,6 @@
       <c r="G459" t="n">
         <v>62</v>
       </c>
-      <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27041,7 +26583,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -27065,7 +26607,6 @@
       <c r="G460" t="n">
         <v>137</v>
       </c>
-      <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27098,7 +26639,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -27122,7 +26663,6 @@
       <c r="G461" t="n">
         <v>62</v>
       </c>
-      <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27155,7 +26695,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -27179,7 +26719,6 @@
       <c r="G462" t="n">
         <v>137</v>
       </c>
-      <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27212,7 +26751,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -27236,7 +26775,6 @@
       <c r="G463" t="n">
         <v>62</v>
       </c>
-      <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27269,7 +26807,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>One-Story Villa</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -27293,7 +26831,6 @@
       <c r="G464" t="n">
         <v>129</v>
       </c>
-      <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/palm-hills-jirian.xlsx
+++ b/data/availability/projects/palm-hills-developments/palm-hills-jirian.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14207,7 +14207,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15361,7 +15361,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -15719,7 +15719,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -17097,7 +17097,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17175,7 +17175,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -18217,7 +18217,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19449,7 +19449,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -20065,7 +20065,7 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -20345,7 +20345,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -20815,7 +20815,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20961,7 +20961,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -21487,7 +21487,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21689,7 +21689,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -21879,7 +21879,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -21935,7 +21935,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -22081,7 +22081,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -22137,7 +22137,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -22215,7 +22215,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -22249,7 +22249,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -22271,7 +22271,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -22361,7 +22361,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -22383,7 +22383,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22529,7 +22529,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -22663,7 +22663,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -22719,7 +22719,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22809,7 +22809,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -22887,7 +22887,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -23055,7 +23055,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -23145,7 +23145,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -23167,7 +23167,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -23223,7 +23223,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -23503,7 +23503,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -23671,7 +23671,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -23705,7 +23705,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -23727,7 +23727,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -23783,7 +23783,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -23817,7 +23817,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -23873,7 +23873,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -23985,7 +23985,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L414" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -24119,7 +24119,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -24265,7 +24265,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -24545,7 +24545,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -24567,7 +24567,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -24601,7 +24601,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -24679,7 +24679,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -24769,7 +24769,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -24791,7 +24791,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -24881,7 +24881,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -24959,7 +24959,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -25049,7 +25049,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -25105,7 +25105,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -25127,7 +25127,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -25273,7 +25273,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -25295,7 +25295,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -25497,7 +25497,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -25721,7 +25721,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -25889,7 +25889,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -25945,7 +25945,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -26001,7 +26001,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
@@ -26023,7 +26023,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -26079,7 +26079,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -26135,7 +26135,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -26247,7 +26247,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -26281,7 +26281,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -26359,7 +26359,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -26471,7 +26471,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -26505,7 +26505,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -26527,7 +26527,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
@@ -26583,7 +26583,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -26617,7 +26617,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>One-Story Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -26841,7 +26841,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
